--- a/data/output/2025/evaluasi_64.xlsx
+++ b/data/output/2025/evaluasi_64.xlsx
@@ -17,6 +17,7 @@
     <sheet name="6404" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="6405" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="6409" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6402" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -844,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +933,444 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>21.46689764214996</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-9.770527060043964</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>49.14870351248301</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.234423391145866</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.569233009990849</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6963975980853266</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2010371648409784</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.70694809968339</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>35.19953444614735</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.016274287005164</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.914991801101161</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.010081741643505</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.825694556730407</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.140799012648023</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -946,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1090,6 +1529,370 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23.05927299174436</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.2233660721998</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6302318257146716</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1520484935915938</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.5526922603962657</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-8.232711429809948</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.138659188760645</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4484463885690554</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.152226883851287</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.586423474004673</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.22697588142188</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.621962409973438</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.62952293643476</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +2107,258 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-5.675589389890785</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.18147571518052</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.512010565659939</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.513758548948003</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.976195080396012</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.88096710525199</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.185816469280929</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.903975055833678</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.002569484088315964</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1318,7 +2373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,6 +2489,230 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.218468735980803</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.23782067968939</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>36.96014047489491</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.043939345528389</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.04615901474774785</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.4530509118375926</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.573041281815916</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.030033786832238</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1448,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1564,6 +2843,258 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5499134757084563</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>19.0558151688677</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.744044992107284</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.370175506514065</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.545038335988978</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.304815250034357</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.585105207001767</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5912225048557482</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.682251378159308</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1578,7 +3109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,6 +3169,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>21.53674665808951</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.061624204646346</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-7.699211001345341</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.109186932355352</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-8.521860440931968</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-4.534005294863519</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.06936826589856</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.093173425565647</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.752810051374504</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1652,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +3551,258 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>22.4206743537692</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.86243748742833</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.80484019352853</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.5357430183902</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.388461065485988</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.810797826507556</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.418084926998532</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.461115145439463</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.367500538183785</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1782,7 +3817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1940,18 +3975,298 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>9.821748745126238</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1841151021845564</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.47359342596967</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.477161443015927</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.171677833664897</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1623713704513421</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-4.078299955940282</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.289441808502073</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.424667738924786</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.230679458020706</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>2.237377669357271</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1968,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2031,6 +4346,174 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.284019690396988</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.406221578586051</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.449863400562217</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.923150643828652</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.342157199442807</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6644121911166693</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
